--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488002_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488002_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7503</v>
+        <v>3.0248</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4361</v>
+        <v>3.5422</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6858</v>
+        <v>-0.5174</v>
       </c>
       <c r="G2" t="n">
         <v>1.9715</v>
@@ -610,13 +610,13 @@
         <v>3.568</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9421</v>
+        <v>0.2167</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4062</v>
+        <v>0.5123</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4641</v>
+        <v>-0.2956</v>
       </c>
       <c r="V2" t="n">
         <v>-1.7403</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2914</v>
+        <v>2.4044</v>
       </c>
       <c r="E3" t="n">
-        <v>3.15</v>
+        <v>1.4804</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1414</v>
+        <v>0.924</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0544</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6496</v>
+        <v>-2.6309</v>
       </c>
       <c r="I3" t="n">
-        <v>0.704</v>
+        <v>2.1294</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7799</v>
+        <v>0.6218</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6192</v>
+        <v>-1.2303</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1607</v>
+        <v>1.8521</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7255</v>
+        <v>-1.1233</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2688</v>
+        <v>-1.4007</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5433</v>
+        <v>0.2774</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7899</v>
+        <v>0.8554</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1036</v>
+        <v>0.5921</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6864</v>
+        <v>0.2633</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9405</v>
+        <v>0.2666</v>
       </c>
       <c r="W3" t="n">
         <v>0.2666</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4158</v>
+        <v>2.2872</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5199</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8959</v>
+        <v>1.7787</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-1.2112</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6309</v>
+        <v>-1.3893</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1294</v>
+        <v>0.1781</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6218</v>
+        <v>0.2519</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2303</v>
+        <v>-0.3223</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8521</v>
+        <v>0.5742</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1233</v>
+        <v>-1.4631</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4007</v>
+        <v>-1.067</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2774</v>
+        <v>-0.3961</v>
       </c>
       <c r="P4" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>3.1716</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8668</v>
+        <v>0.4984</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.1617</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2352</v>
+        <v>0.3367</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2666</v>
+        <v>1.8107</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2666</v>
+        <v>2.0772</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0139</v>
+        <v>2.1313</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0387</v>
+        <v>1.99</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9752</v>
+        <v>0.1414</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2112</v>
+        <v>0.0544</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3893</v>
+        <v>-0.6496</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1781</v>
+        <v>0.704</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2519</v>
+        <v>0.7799</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3223</v>
+        <v>0.6192</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5742</v>
+        <v>0.1607</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4631</v>
+        <v>-0.7255</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.067</v>
+        <v>-1.2688</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3961</v>
+        <v>0.5433</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1716</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2251</v>
+        <v>1.6299</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3082</v>
+        <v>0.9435</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5333</v>
+        <v>0.6864</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8107</v>
+        <v>-0.9405</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0772</v>
+        <v>0.2666</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.712</v>
+        <v>-0.2768</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4674</v>
+        <v>0.388</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7554999999999999</v>
+        <v>-0.6647</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.5135</v>
+        <v>0.3656</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2923</v>
+        <v>-0.5738</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2212</v>
+        <v>0.9394</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5264</v>
+        <v>1.8151</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.369</v>
+        <v>0.4854</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1574</v>
+        <v>1.3298</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9871</v>
+        <v>-1.4495</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9233</v>
+        <v>-1.0591</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0638</v>
+        <v>-0.3904</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3787</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>-4.9556</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3698</v>
+        <v>2.7751</v>
       </c>
       <c r="S7" t="n">
-        <v>1.293</v>
+        <v>1.0049</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0501</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2429</v>
+        <v>0.4239</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8701</v>
+        <v>0.5331</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.9474</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8701</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.791</v>
+        <v>-0.3201</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4332</v>
+        <v>-2.5706</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3578</v>
+        <v>2.2505</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0732</v>
+        <v>-6.0493</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1072</v>
+        <v>-0.6526</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1804</v>
+        <v>-5.3968</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1781</v>
+        <v>-4.5374</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4912</v>
+        <v>-0.4704</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6869</v>
+        <v>-4.067</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2513</v>
+        <v>-1.5119</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3839</v>
+        <v>-0.1822</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8674</v>
+        <v>-1.3298</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7929</v>
+        <v>3.3698</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7751</v>
+        <v>3.3698</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6964</v>
+        <v>0.5488</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3709</v>
+        <v>0.1562</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3255</v>
+        <v>0.3927</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2071</v>
+        <v>1.8107</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9681</v>
+        <v>-0.8366</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8972</v>
+        <v>-1.6482</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9291</v>
+        <v>0.8116</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2776</v>
+        <v>-3.5135</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4774</v>
+        <v>-1.2923</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8002</v>
+        <v>-2.2212</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6883</v>
+        <v>-1.5264</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5857</v>
+        <v>-0.369</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.274</v>
+        <v>-1.1574</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5893</v>
+        <v>-1.9871</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0631</v>
+        <v>-0.9233</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5262</v>
+        <v>-1.0638</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9822</v>
+        <v>3.3698</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0429</v>
+        <v>1.1683</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5068</v>
+        <v>0.8693</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5362</v>
+        <v>0.2991</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2666</v>
+        <v>-0.8701</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1209</v>
+        <v>-0.9147</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5123</v>
+        <v>-0.4727</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6086</v>
+        <v>-0.442</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3656</v>
+        <v>-1.0732</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5738</v>
+        <v>0.1072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9394</v>
+        <v>-1.1804</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8151</v>
+        <v>1.1781</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4854</v>
+        <v>0.4912</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3298</v>
+        <v>0.6869</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4495</v>
+        <v>-2.2513</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0591</v>
+        <v>-0.3839</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3904</v>
+        <v>-1.8674</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1805</v>
+        <v>0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.9556</v>
+        <v>-1.9822</v>
       </c>
       <c r="R10" t="n">
         <v>2.7751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1608</v>
+        <v>0.5727</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3192</v>
+        <v>0.3315</v>
       </c>
       <c r="U10" t="n">
-        <v>0.48</v>
+        <v>0.2412</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5331</v>
+        <v>-1.2071</v>
       </c>
       <c r="W10" t="n">
-        <v>2.9474</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5759</v>
+        <v>-1.3621</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7141</v>
+        <v>-2.0385</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1382</v>
+        <v>0.6764</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.0493</v>
+        <v>-2.2776</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6526</v>
+        <v>-0.4774</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.3968</v>
+        <v>-1.8002</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.5374</v>
+        <v>-0.6883</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4704</v>
+        <v>0.5857</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.067</v>
+        <v>-1.274</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5119</v>
+        <v>-1.5893</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1822</v>
+        <v>-1.0631</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3298</v>
+        <v>-0.5262</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3698</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>3.3698</v>
+        <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.707</v>
+        <v>0.6489</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9873</v>
+        <v>0.3654</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2803</v>
+        <v>0.2835</v>
       </c>
       <c r="V11" t="n">
-        <v>1.8107</v>
+        <v>0.2666</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8107</v>
+        <v>0.2666</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3828</v>
+        <v>-3.2808</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5765</v>
+        <v>-2.6992</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8063</v>
+        <v>-0.5816</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8572</v>
@@ -1390,13 +1390,13 @@
         <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.922</v>
+        <v>0.18</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8001</v>
+        <v>0.0772</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1219</v>
+        <v>0.1027</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2071</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.731399999999999</v>
+        <v>4.6673</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6452999999999993</v>
+        <v>0.2907000000000015</v>
       </c>
       <c r="F13" t="n">
-        <v>4.376799999999999</v>
+        <v>4.3769</v>
       </c>
       <c r="G13" t="n">
         <v>-12.2813</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.1123</v>
+        <v>-6.112300000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-6.1692</v>
@@ -1447,7 +1447,7 @@
         <v>3.1602</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2280000000000009</v>
+        <v>-0.2280000000000004</v>
       </c>
       <c r="M13" t="n">
         <v>-15.2136</v>
@@ -1468,13 +1468,13 @@
         <v>25.769</v>
       </c>
       <c r="S13" t="n">
-        <v>6.388</v>
+        <v>7.324</v>
       </c>
       <c r="T13" t="n">
-        <v>3.654399999999999</v>
+        <v>4.590300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7338</v>
+        <v>2.7339</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2774</v>
@@ -1483,7 +1483,7 @@
         <v>7.6351</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.9125</v>
+        <v>-8.912500000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8077</v>
+        <v>2.2087</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7934</v>
+        <v>0.581</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0142</v>
+        <v>1.6277</v>
       </c>
       <c r="G15" t="n">
-        <v>7.0437</v>
+        <v>3.6032</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6924</v>
+        <v>2.3942</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3513</v>
+        <v>1.209</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3667</v>
+        <v>2.9437</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5872</v>
+        <v>2.3008</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7795</v>
+        <v>0.6428</v>
       </c>
       <c r="M15" t="n">
-        <v>0.677</v>
+        <v>0.6595</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1052</v>
+        <v>0.0934</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5718</v>
+        <v>0.5661</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.7574</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.136</v>
+        <v>-2.9733</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3787</v>
+        <v>2.5769</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5118</v>
+        <v>-1.161</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8515</v>
+        <v>-0.5964</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6603</v>
+        <v>-0.5646</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0331</v>
+        <v>0.163</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4142</v>
+        <v>1.2071</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3811</v>
+        <v>-1.0442</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4244</v>
+        <v>2.2034</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3773</v>
+        <v>0.9971</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0472</v>
+        <v>1.2062</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6032</v>
+        <v>7.0437</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3942</v>
+        <v>4.6924</v>
       </c>
       <c r="I16" t="n">
-        <v>1.209</v>
+        <v>2.3513</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9437</v>
+        <v>6.3667</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3008</v>
+        <v>4.5872</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6428</v>
+        <v>1.7795</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6595</v>
+        <v>0.677</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0934</v>
+        <v>0.1052</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5661</v>
+        <v>0.5718</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3964</v>
+        <v>-4.7574</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9733</v>
+        <v>-7.136</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5769</v>
+        <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9452</v>
+        <v>-1.1161</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8001</v>
+        <v>-0.6478</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1451</v>
+        <v>-0.4683</v>
       </c>
       <c r="V16" t="n">
-        <v>0.163</v>
+        <v>1.0331</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2071</v>
+        <v>2.4142</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0442</v>
+        <v>-1.3811</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5235</v>
+        <v>0.7155</v>
       </c>
       <c r="E17" t="n">
         <v>0.0452</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4783</v>
+        <v>0.6702</v>
       </c>
       <c r="G17" t="n">
         <v>0.3605</v>
@@ -1780,13 +1780,13 @@
         <v>0.7929</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5793</v>
+        <v>-0.3873</v>
       </c>
       <c r="T17" t="n">
         <v>-0.312</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2673</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0.9405</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1335</v>
+        <v>0.3558</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7971</v>
+        <v>-1.6037</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6637</v>
+        <v>1.9595</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5867</v>
+        <v>2.3266</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6097</v>
+        <v>-1.7904</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0231</v>
+        <v>4.117</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8516</v>
+        <v>1.7445</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4464</v>
+        <v>-0.8671</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5949</v>
+        <v>2.6115</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7351</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1633</v>
+        <v>-0.9233</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5718</v>
+        <v>1.5055</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7929</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q18" t="n">
         <v>-3.1716</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3787</v>
+        <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1496</v>
+        <v>-0.6516</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4771</v>
+        <v>-0.4432</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3275</v>
+        <v>-0.2085</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7776</v>
+        <v>0.2666</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GARCIA TEJON</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1869</v>
+        <v>-0.3007</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9846</v>
+        <v>-0.0624</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7977</v>
+        <v>-0.2383</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8707</v>
+        <v>-0.1961</v>
       </c>
       <c r="H19" t="n">
-        <v>1.682</v>
+        <v>-0.2018</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8113</v>
+        <v>0.0057</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3445</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7825</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4381</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4738</v>
+        <v>-0.1961</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1005</v>
+        <v>-0.2018</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3733</v>
+        <v>0.0057</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2285</v>
+        <v>-0.1046</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0365</v>
+        <v>-0.0624</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2651</v>
+        <v>-0.0422</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6961000000000001</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3569</v>
+        <v>-0.475</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0624</v>
+        <v>-2.7971</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2945</v>
+        <v>2.3222</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1961</v>
+        <v>1.5867</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2018</v>
+        <v>1.6097</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0057</v>
+        <v>-0.0231</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.8516</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.4464</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.5949</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1961</v>
+        <v>0.7351</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2018</v>
+        <v>0.1633</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0057</v>
+        <v>0.5718</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1608</v>
+        <v>-0.4912</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0624</v>
+        <v>-0.4771</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0984</v>
+        <v>-0.014</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.7776</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.7776</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>A. GARCIA TEJON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5303</v>
+        <v>-0.6303</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9093</v>
+        <v>-2.0865</v>
       </c>
       <c r="F21" t="n">
-        <v>1.379</v>
+        <v>1.4562</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3266</v>
+        <v>0.8707</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7904</v>
+        <v>1.682</v>
       </c>
       <c r="I21" t="n">
-        <v>4.117</v>
+        <v>-0.8113</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7445</v>
+        <v>1.3445</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8671</v>
+        <v>1.7825</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6115</v>
+        <v>-0.4381</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5822000000000001</v>
+        <v>-0.4738</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9233</v>
+        <v>-0.1005</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5055</v>
+        <v>-0.3733</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5858</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1716</v>
+        <v>-4.1627</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5378</v>
+        <v>-0.2149</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7488</v>
+        <v>-0.1384</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.789</v>
+        <v>-0.0764</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2666</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2666</v>
+        <v>0.8701</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-1.3295</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4441</v>
+        <v>1.1671</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2219</v>
+        <v>-2.4966</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7755</v>
+        <v>1.568</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6506</v>
+        <v>0.2461</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.125</v>
+        <v>1.322</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.454</v>
+        <v>3.4796</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8552</v>
+        <v>1.507</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5988</v>
+        <v>1.9726</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3215</v>
+        <v>-1.9115</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7953</v>
+        <v>-1.2609</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5262</v>
+        <v>-0.6506</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5947</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>1.196</v>
+        <v>-0.5011</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4244</v>
+        <v>-0.132</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2284</v>
+        <v>-0.369</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2071</v>
+        <v>-1.2071</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6309</v>
+        <v>-1.5748</v>
       </c>
       <c r="E23" t="n">
         <v>-0.6681</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9628</v>
+        <v>-0.9067</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4128</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0485</v>
+        <v>0.1046</v>
       </c>
       <c r="T23" t="n">
         <v>0.011</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2666</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9992</v>
+        <v>-1.8186</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2768</v>
+        <v>-0.6764</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7224</v>
+        <v>-1.1422</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3795</v>
+        <v>-3.7755</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5541</v>
+        <v>-2.6506</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9337</v>
+        <v>-1.125</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3425</v>
+        <v>-2.454</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3367</v>
+        <v>-1.8552</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6791</v>
+        <v>-0.5988</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0371</v>
+        <v>-1.3215</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2175</v>
+        <v>-0.7953</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2545</v>
+        <v>-0.5262</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.5947</v>
+        <v>0.5947</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8509</v>
+        <v>0.1551</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4257</v>
+        <v>0.3039</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4252</v>
+        <v>-0.1488</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.174</v>
+        <v>1.2071</v>
       </c>
       <c r="W24" t="n">
         <v>1.4737</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6477</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0413</v>
+        <v>-1.8412</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7596000000000001</v>
+        <v>-1.1749</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8009</v>
+        <v>-0.6663</v>
       </c>
       <c r="G25" t="n">
-        <v>1.568</v>
+        <v>-0.3795</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2461</v>
+        <v>0.5541</v>
       </c>
       <c r="I25" t="n">
-        <v>1.322</v>
+        <v>-0.9337</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4796</v>
+        <v>-0.3425</v>
       </c>
       <c r="K25" t="n">
-        <v>1.507</v>
+        <v>0.3367</v>
       </c>
       <c r="L25" t="n">
-        <v>1.9726</v>
+        <v>-0.6791</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9115</v>
+        <v>-0.0371</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2609</v>
+        <v>0.2175</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6506</v>
+        <v>-0.2545</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1893</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1805</v>
+        <v>-1.9822</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2129</v>
+        <v>-0.6929</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5395</v>
+        <v>-0.3239</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6733</v>
+        <v>-0.369</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2071</v>
+        <v>-0.174</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2071</v>
+        <v>-1.6477</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.2463</v>
+        <v>-2.3025</v>
       </c>
       <c r="E26" t="n">
         <v>-0.5141</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7322</v>
+        <v>-1.7883</v>
       </c>
       <c r="G26" t="n">
         <v>-1.7301</v>
@@ -2482,13 +2482,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0312</v>
       </c>
       <c r="T26" t="n">
         <v>0.08450000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0029</v>
+        <v>-0.0533</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6036</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.731400000000001</v>
+        <v>-2.3732</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.3768</v>
+        <v>-4.376799999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6453999999999998</v>
+        <v>2.0036</v>
       </c>
       <c r="G27" t="n">
         <v>12.2814</v>
       </c>
       <c r="H27" t="n">
-        <v>6.112000000000002</v>
+        <v>6.112</v>
       </c>
       <c r="I27" t="n">
         <v>6.1691</v>
@@ -2548,7 +2548,7 @@
         <v>-3.1602</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2280999999999997</v>
+        <v>0.2281000000000002</v>
       </c>
       <c r="P27" t="n">
         <v>-10.9022</v>
@@ -2560,13 +2560,13 @@
         <v>14.8669</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.387900000000002</v>
+        <v>-5.0298</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.7337</v>
+        <v>-2.7338</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.6541</v>
+        <v>-2.2958</v>
       </c>
       <c r="V27" t="n">
         <v>1.2775</v>
